--- a/test.xlsx
+++ b/test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="15960" windowHeight="9870"/>
   </bookViews>
   <sheets>
     <sheet name="创建用户" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <si>
     <t>id</t>
   </si>
@@ -55,19 +55,37 @@
     <t>sql</t>
   </si>
   <si>
-    <t>get_all_purview_list_02</t>
+    <t>allureEpic</t>
+  </si>
+  <si>
+    <t>商城平台接口</t>
+  </si>
+  <si>
+    <t>allureFeature</t>
+  </si>
+  <si>
+    <t>用户管理</t>
+  </si>
+  <si>
+    <t>allureStory</t>
+  </si>
+  <si>
+    <t>修改用户状态</t>
+  </si>
+  <si>
+    <t>update_user_status_01</t>
   </si>
   <si>
     <t>${{host()}}</t>
   </si>
   <si>
-    <t>/api/private/v1/rights/list</t>
-  </si>
-  <si>
-    <t>GET</t>
-  </si>
-  <si>
-    <t>获取所有权限列表展示成功</t>
+    <t>/api/private/v1/users/$cache{id}/state/true</t>
+  </si>
+  <si>
+    <t>PUT</t>
+  </si>
+  <si>
+    <t>修改用户状态成功</t>
   </si>
   <si>
     <t>{'Authorization': '$cache{token}'}</t>
@@ -76,16 +94,31 @@
     <t>None</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>[{'case_id': 'create_user_03', 'dependent_data': [{'dependent_type': 'response', 'jsonpath': '$.data.id', 'set_cache': 'id', 'replace_key': None}]}]</t>
+  </si>
+  <si>
+    <t>{'errorInfo_1': {'jsonpath': '$.data.mg_state', 'type': '==', 'value': 1, 'AssertType': None}, 'errorInfo_2': {'jsonpath': '$.meta.msg', 'type': '==', 'value': '设置状态成功', 'AssertType': None}, 'errorStatus': {'jsonpath': '$.meta.status', 'type': '==', 'value': 200, 'AssertType': None}}</t>
+  </si>
+  <si>
+    <t>update_user_status_02</t>
+  </si>
+  <si>
+    <t>修改用户状态失败（id为字符串）</t>
+  </si>
+  <si>
     <t>TRUE</t>
   </si>
   <si>
-    <t>{'errorInfo_1': {'jsonpath': '$.data.mg_state', 'type': '==', 'value': 1, 'AssertType': None}, 'errorInfo_2': {'jsonpath': '$.meta.msg', 'type': '==', 'value': '设置状态成功', 'AssertType': None}, 'errorStatus': {'jsonpath': '$.meta.status', 'type': '==', 'value': 200, 'AssertType': None}}</t>
-  </si>
-  <si>
-    <t>Authorization: $cache{token}</t>
-  </si>
-  <si>
-    <t>get_all_purview_list_03</t>
+    <t>{'errorStatus': {'jsonpath': '$.meta.status', 'type': '==', 'value': 400, 'AssertType': None}, 'errorInfo': {'jsonpath': '$.meta.msg', 'type': '==', 'value': '用户ID必须是数字', 'AssertType': None}}</t>
+  </si>
+  <si>
+    <t>update_user_status_03</t>
+  </si>
+  <si>
+    <t>修改用户状态失败（id包含特殊字符）</t>
   </si>
 </sst>
 </file>
@@ -722,15 +755,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1066,10 +1096,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="1" max="1" width="12.125" customWidth="1"/>
     <col min="2" max="2" width="16.875" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="10.625" customWidth="1"/>
@@ -1078,8 +1108,8 @@
     <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="12.625" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="7.5" customWidth="1"/>
-    <col min="11" max="11" width="4.5" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="11" max="11" width="23.625" customWidth="1"/>
     <col min="12" max="12" width="69.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1123,601 +1153,643 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-    </row>
-    <row r="2" ht="41" customHeight="1" spans="1:13">
-      <c r="A2" s="2" t="s">
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+    </row>
+    <row r="2" ht="35" customHeight="1" spans="1:16">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+    </row>
+    <row r="3" ht="41" customHeight="1" spans="1:13">
+      <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:13">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="4"/>
+    </row>
+    <row r="4" ht="62" customHeight="1" spans="1:13">
+      <c r="A4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="E4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="4"/>
+    </row>
+    <row r="5" ht="105" customHeight="1" spans="1:13">
+      <c r="A5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="5"/>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:13">
-      <c r="A4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="5"/>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:13">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="E5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="4"/>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:13">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:13">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:13">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:13">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:13">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:13">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:15">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:13">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:13">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
+      <c r="M12" s="4"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:15">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:13">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:13">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:13">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:13">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:13">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:13">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:13">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:13">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:13">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:13">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:13">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:13">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:13">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:13">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:13">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:13">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:13">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:13">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
     </row>
     <row r="32" ht="18" customHeight="1" spans="1:13">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
     </row>
     <row r="33" ht="18" customHeight="1" spans="1:13">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:13">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:13">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:13">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
     </row>
     <row r="37" ht="18" customHeight="1" spans="1:13">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:13">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
